--- a/data/trans_orig/P43A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P43A-Edad-trans_orig.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>14005</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>14005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,46%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>21670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>21670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24934</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24934</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>33481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>33481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68967</t>
+          <t>67691</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>99093</t>
+          <t>96979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68967</t>
+          <t>67691</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99093</t>
+          <t>96979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51032</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78426</t>
+          <t>78655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51032</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78426</t>
+          <t>78655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>30884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54742</t>
+          <t>54313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>30884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54742</t>
+          <t>54313</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52605</t>
+          <t>52634</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52605</t>
+          <t>52634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86542</t>
+          <t>86117</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117867</t>
+          <t>117284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86542</t>
+          <t>86117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117867</t>
+          <t>117284</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81514</t>
+          <t>83074</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>115825</t>
+          <t>116186</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81514</t>
+          <t>83074</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115825</t>
+          <t>116186</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63208</t>
+          <t>62479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92274</t>
+          <t>94133</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63208</t>
+          <t>62479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92274</t>
+          <t>94133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60036</t>
+          <t>57935</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60036</t>
+          <t>57935</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>121591</t>
+          <t>121659</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153328</t>
+          <t>155773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121591</t>
+          <t>121659</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>153328</t>
+          <t>155773</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,7%</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52453</t>
+          <t>52018</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79794</t>
+          <t>80126</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52453</t>
+          <t>52018</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79794</t>
+          <t>80126</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41165</t>
+          <t>40176</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>66720</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41165</t>
+          <t>40176</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>66720</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>77225</t>
+          <t>77623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104404</t>
+          <t>104853</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>77225</t>
+          <t>77623</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104404</t>
+          <t>104853</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56694</t>
+          <t>55478</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82089</t>
+          <t>80496</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56694</t>
+          <t>55478</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82089</t>
+          <t>80496</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48559</t>
+          <t>48186</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48559</t>
+          <t>48186</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>26412</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>26412</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54769</t>
+          <t>55229</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>54769</t>
+          <t>55229</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4233,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39954</t>
+          <t>39655</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39954</t>
+          <t>39655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -4787,12 +4787,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>37346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63393</t>
+          <t>64825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>37346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63393</t>
+          <t>64825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -4865,12 +4865,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66358</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95351</t>
+          <t>95048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66358</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95351</t>
+          <t>95048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4915,12 +4915,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -4943,12 +4943,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44473</t>
+          <t>45514</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71943</t>
+          <t>71830</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44473</t>
+          <t>45514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71943</t>
+          <t>71830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34982</t>
+          <t>36419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59781</t>
+          <t>61471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34982</t>
+          <t>36419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59781</t>
+          <t>61471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>60530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>60530</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -5259,12 +5259,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137467</t>
+          <t>137052</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178319</t>
+          <t>180810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137467</t>
+          <t>137052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178319</t>
+          <t>180810</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>117977</t>
+          <t>118744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157340</t>
+          <t>160025</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>117977</t>
+          <t>118744</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>157340</t>
+          <t>160025</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -5415,12 +5415,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>55488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86281</t>
+          <t>87283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>55488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86281</t>
+          <t>87283</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -5575,12 +5575,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>27882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>27882</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>178451</t>
+          <t>177185</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>218290</t>
+          <t>218333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>178451</t>
+          <t>177185</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218290</t>
+          <t>218333</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102592</t>
+          <t>104020</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>141022</t>
+          <t>142165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102592</t>
+          <t>104020</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>141022</t>
+          <t>142165</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>56303</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>86698</t>
+          <t>85688</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56303</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>86698</t>
+          <t>85688</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62725</t>
+          <t>64835</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93665</t>
+          <t>93777</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62725</t>
+          <t>64835</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93665</t>
+          <t>93777</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -6047,12 +6047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106380</t>
+          <t>106103</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>141568</t>
+          <t>139591</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>106380</t>
+          <t>106103</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141568</t>
+          <t>139591</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,61%</t>
         </is>
       </c>
     </row>
@@ -6125,12 +6125,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58624</t>
+          <t>59189</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>89174</t>
+          <t>88692</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>58624</t>
+          <t>59189</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>89174</t>
+          <t>88692</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6203,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36099</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36099</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -6363,12 +6363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>118383</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>149061</t>
+          <t>150053</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>118383</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149061</t>
+          <t>150053</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>55769</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>55769</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -6597,12 +6597,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>308016</t>
+          <t>309091</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>378446</t>
+          <t>377771</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>308016</t>
+          <t>309091</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>378446</t>
+          <t>377771</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>597342</t>
+          <t>598796</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>677877</t>
+          <t>677245</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>597342</t>
+          <t>598796</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>677877</t>
+          <t>677245</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>403737</t>
+          <t>406435</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>477365</t>
+          <t>480577</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>403737</t>
+          <t>406435</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>477365</t>
+          <t>480577</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>212358</t>
+          <t>213239</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>274247</t>
+          <t>272911</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>212358</t>
+          <t>213239</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>274247</t>
+          <t>272911</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -7403,12 +7403,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>39349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7832,12 +7832,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>39349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31461</t>
+          <t>31569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7890,12 +7890,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7910,12 +7910,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31461</t>
+          <t>31569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -7953,12 +7953,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7988,12 +7988,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31790</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55123</t>
+          <t>53491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8128,12 +8128,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31790</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55123</t>
+          <t>53491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -8191,12 +8191,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72243</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>99836</t>
+          <t>100778</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72243</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99836</t>
+          <t>100778</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8241,12 +8241,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83844</t>
+          <t>84539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83844</t>
+          <t>84539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -8347,12 +8347,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>39987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>39987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -8507,12 +8507,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40480</t>
+          <t>42006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67479</t>
+          <t>70557</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40480</t>
+          <t>42006</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67479</t>
+          <t>70557</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -8585,12 +8585,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165694</t>
+          <t>162426</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205714</t>
+          <t>207233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8620,12 +8620,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165694</t>
+          <t>162426</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205714</t>
+          <t>207233</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8635,12 +8635,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -8663,12 +8663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>103802</t>
+          <t>102656</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142787</t>
+          <t>140110</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103802</t>
+          <t>102656</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>142787</t>
+          <t>140110</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51863</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83481</t>
+          <t>84558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51863</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83481</t>
+          <t>84558</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>48246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79687</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>48246</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>79687</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>194215</t>
+          <t>193730</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>240436</t>
+          <t>239607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>194215</t>
+          <t>193730</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>240436</t>
+          <t>239607</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9029,12 +9029,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -9057,12 +9057,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>87257</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126280</t>
+          <t>126448</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>87257</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126280</t>
+          <t>126448</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -9135,12 +9135,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47525</t>
+          <t>47819</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>78991</t>
+          <t>78421</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9170,12 +9170,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>47525</t>
+          <t>47819</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>78991</t>
+          <t>78421</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -9295,12 +9295,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>68554</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>101506</t>
+          <t>97943</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>68554</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>101506</t>
+          <t>97943</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118023</t>
+          <t>118764</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>154133</t>
+          <t>155479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>118023</t>
+          <t>118764</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>154133</t>
+          <t>155479</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -9451,12 +9451,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>51332</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>79745</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>51332</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>79745</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -9529,12 +9529,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>25461</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50456</t>
+          <t>49956</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>25461</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50456</t>
+          <t>49956</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>157829</t>
+          <t>157826</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>188727</t>
+          <t>189344</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>157829</t>
+          <t>157826</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>188727</t>
+          <t>189344</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -9767,12 +9767,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>28312</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>54911</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>28312</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>54911</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -9845,12 +9845,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>31348</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>31348</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -10083,12 +10083,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>393266</t>
+          <t>388794</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>465610</t>
+          <t>467388</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10118,12 +10118,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>393266</t>
+          <t>388794</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>465610</t>
+          <t>467388</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>658788</t>
+          <t>664508</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>746128</t>
+          <t>747576</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>658788</t>
+          <t>664508</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>746128</t>
+          <t>747576</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -10239,12 +10239,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>378201</t>
+          <t>376572</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>450296</t>
+          <t>450291</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>378201</t>
+          <t>376572</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>450296</t>
+          <t>450291</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>184251</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>237087</t>
+          <t>239535</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10332,12 +10332,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>184251</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>237087</t>
+          <t>239535</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10367,12 +10367,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>47,3%</t>
         </is>
       </c>
     </row>
@@ -10724,32 +10724,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10759,32 +10759,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -10802,32 +10802,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10837,32 +10837,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -10958,17 +10958,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -11118,32 +11118,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11153,32 +11153,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -11196,32 +11196,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11231,32 +11231,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -11274,32 +11274,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11309,32 +11309,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -11352,17 +11352,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50580</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50580</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50580</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11387,17 +11387,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50580</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50580</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50580</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11434,32 +11434,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>37298</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28691</t>
+          <t>31867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11469,32 +11469,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37298</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28691</t>
+          <t>31867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -11512,32 +11512,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>45436</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11547,32 +11547,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>45436</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -11590,32 +11590,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38834</t>
+          <t>46175</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30484</t>
+          <t>37687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47340</t>
+          <t>55611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11625,32 +11625,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38834</t>
+          <t>46175</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30484</t>
+          <t>37687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47340</t>
+          <t>55611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -11668,32 +11668,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23904</t>
+          <t>26750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11703,32 +11703,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23904</t>
+          <t>26750</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -11746,17 +11746,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11828,32 +11828,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>76031</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44682</t>
+          <t>35137</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>166085</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11863,32 +11863,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76031</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44682</t>
+          <t>35137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166085</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -11906,32 +11906,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>90609</t>
+          <t>101835</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61133</t>
+          <t>88498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107197</t>
+          <t>115249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11941,32 +11941,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>90609</t>
+          <t>101835</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61133</t>
+          <t>88498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107197</t>
+          <t>115249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -11984,32 +11984,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>99505</t>
+          <t>105685</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65831</t>
+          <t>92399</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>117729</t>
+          <t>117803</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12019,32 +12019,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>99505</t>
+          <t>105685</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65831</t>
+          <t>92399</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>117729</t>
+          <t>117803</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -12062,32 +12062,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>60156</t>
+          <t>64052</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41225</t>
+          <t>53188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73549</t>
+          <t>75120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12097,32 +12097,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60156</t>
+          <t>64052</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41225</t>
+          <t>53188</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73549</t>
+          <t>75120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -12140,17 +12140,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>326301</t>
+          <t>315836</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>326301</t>
+          <t>315836</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>326301</t>
+          <t>315836</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12175,17 +12175,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>326301</t>
+          <t>315836</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326301</t>
+          <t>315836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326301</t>
+          <t>315836</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12222,32 +12222,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>49103</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40519</t>
+          <t>43620</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59439</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12257,32 +12257,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>49103</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40519</t>
+          <t>43620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59439</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -12300,32 +12300,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>133483</t>
+          <t>146173</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>121921</t>
+          <t>132933</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147602</t>
+          <t>161296</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12335,32 +12335,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>133483</t>
+          <t>146173</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121921</t>
+          <t>132933</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147602</t>
+          <t>161296</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -12378,32 +12378,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>93779</t>
+          <t>104313</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81728</t>
+          <t>91283</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105451</t>
+          <t>117875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12413,32 +12413,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>93779</t>
+          <t>104313</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81728</t>
+          <t>91283</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105451</t>
+          <t>117875</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -12456,32 +12456,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>45184</t>
+          <t>49689</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>39953</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>59898</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12491,32 +12491,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>45184</t>
+          <t>49689</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>39953</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>59898</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -12534,17 +12534,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>321549</t>
+          <t>354521</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>321549</t>
+          <t>354521</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>321549</t>
+          <t>354521</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12569,17 +12569,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>321549</t>
+          <t>354521</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>321549</t>
+          <t>354521</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>321549</t>
+          <t>354521</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12616,32 +12616,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>86902</t>
+          <t>93371</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31463</t>
+          <t>83247</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>158892</t>
+          <t>104815</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12651,32 +12651,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>86902</t>
+          <t>93371</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31463</t>
+          <t>83247</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>158892</t>
+          <t>104815</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -12694,32 +12694,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>308916</t>
+          <t>116158</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>175941</t>
+          <t>103831</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>417139</t>
+          <t>127549</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12729,32 +12729,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>308916</t>
+          <t>116158</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>175941</t>
+          <t>103831</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>417139</t>
+          <t>127549</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -12772,32 +12772,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>58146</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>49267</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>98558</t>
+          <t>69313</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12807,32 +12807,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>58146</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>49267</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98558</t>
+          <t>69313</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -12850,32 +12850,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>25938</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>21668</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>36278</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12885,32 +12885,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>25938</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>21668</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>36278</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -12928,17 +12928,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>474938</t>
+          <t>295363</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>474938</t>
+          <t>295363</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>474938</t>
+          <t>295363</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12963,17 +12963,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>474938</t>
+          <t>295363</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>474938</t>
+          <t>295363</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>474938</t>
+          <t>295363</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13010,32 +13010,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>217190</t>
+          <t>234371</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>207962</t>
+          <t>223821</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>225244</t>
+          <t>243518</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13045,32 +13045,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>217190</t>
+          <t>234371</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>207962</t>
+          <t>223821</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>225244</t>
+          <t>243518</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -13088,32 +13088,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>27853</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21411</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>40077</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13123,32 +13123,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>27853</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>21411</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>40077</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -13166,32 +13166,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>863</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>863</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -13322,17 +13322,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>257580</t>
+          <t>279609</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>257580</t>
+          <t>279609</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>257580</t>
+          <t>279609</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13357,17 +13357,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>257580</t>
+          <t>279609</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>257580</t>
+          <t>279609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>257580</t>
+          <t>279609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13404,32 +13404,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>481689</t>
+          <t>482169</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>322657</t>
+          <t>451440</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>574275</t>
+          <t>509621</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -13439,32 +13439,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>481689</t>
+          <t>482169</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>322657</t>
+          <t>451440</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>574275</t>
+          <t>509621</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -13482,32 +13482,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>620565</t>
+          <t>457782</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>466801</t>
+          <t>431618</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>956590</t>
+          <t>487799</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -13517,32 +13517,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>620565</t>
+          <t>457782</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>466801</t>
+          <t>431618</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>956590</t>
+          <t>487799</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -13560,32 +13560,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>309699</t>
+          <t>341211</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>202472</t>
+          <t>313123</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>364691</t>
+          <t>367224</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -13595,32 +13595,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>309699</t>
+          <t>341211</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>202472</t>
+          <t>313123</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>364691</t>
+          <t>367224</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -13638,32 +13638,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>109433</t>
+          <t>162379</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>199522</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -13673,32 +13673,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>109433</t>
+          <t>162379</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>199522</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -13716,17 +13716,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -13751,17 +13751,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
